--- a/data/extracted/series/fearnleys_md_master_econometric_series.xlsx
+++ b/data/extracted/series/fearnleys_md_master_econometric_series.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>47 rows (97.9% yield, 1 dark-mode discarded)</t>
+          <t>48 rows (97.9% yield, 1 dark-mode discarded)</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>112 rows</t>
+          <t>115 rows</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>40 rows</t>
+          <t>43 rows</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L48"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3873,6 +3873,58 @@
       <c r="L48" s="2" t="inlineStr">
         <is>
           <t>190c6f48-0d96-416d-8157-70474979f10c</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>BULK</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Fearnleys Dry Bulk Weekly</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>10273.97</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>10616.44</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>-20.82</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>2 Months</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>P5 vs Newcastle Coal Futures Spread Lead</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>P5 vs Newcastle Coal Futures Spread Lead.png</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>eaa9d164-ef32-4861-b3c3-7f93faf786de</t>
         </is>
       </c>
     </row>
@@ -7553,7 +7605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K113"/>
+  <dimension ref="A1:K116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13338,6 +13390,159 @@
         </is>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>BULK</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Fearnleys Dry Bulk Weekly</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>P5TC vs Pacific Tightness Indicator Zoom In.png</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Indicator Metric</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>452</v>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Freight Benchmark</t>
+        </is>
+      </c>
+      <c r="I114" s="3" t="n">
+        <v>296</v>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>Concurrent</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>eaa9d164-ef32-4861-b3c3-7f93faf786de</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>BULK</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Fearnleys Dry Bulk Weekly</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>P6 vs SATL Tightness Zoom In.png</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>South Atlantic Vessel Count</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>198.9</v>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>P6 / BCI5TC Index USD/day</t>
+        </is>
+      </c>
+      <c r="I115" s="3" t="n">
+        <v>20767.9</v>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>1 Month Lead</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>eaa9d164-ef32-4861-b3c3-7f93faf786de</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>BULK</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Fearnleys Dry Bulk Weekly</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>supraultra ballaster laden vessel ratio.png</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Indicator Metric</t>
+        </is>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>512</v>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>Freight Benchmark</t>
+        </is>
+      </c>
+      <c r="I116" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>Concurrent</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>eaa9d164-ef32-4861-b3c3-7f93faf786de</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13349,7 +13554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -15344,6 +15549,151 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>BULK</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Fearnleys Dry Bulk Weekly</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Panamax/Kamsarmax</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>3.1%</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>4.2%</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v/>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>eaa9d164-ef32-4861-b3c3-7f93faf786de</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>BULK</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Fearnleys Dry Bulk Weekly</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Supramax/Ultramax</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>eaa9d164-ef32-4861-b3c3-7f93faf786de</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>BULK</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Fearnleys Dry Bulk Weekly</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Handysize</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>eaa9d164-ef32-4861-b3c3-7f93faf786de</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
